--- a/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>36,08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>33,45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,65</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>206,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>137,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>119,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,68; 41,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,66; 39,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,26; 41,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,28; 29,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>149,86; 281,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95,11; 187,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,67; 166,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,57; 70,85</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>43,88</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>38,11</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>29,12</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>103,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,03; 48,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,42; 42,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,39; 33,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,93; 32,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,85; 124,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,44; 91,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,28; 60,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,13; 52,25</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>52,06</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>37,02</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>29,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>126,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,32; 56,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,56; 41,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,07; 32,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,39; 24,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>104,63; 149,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,84; 77,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,83; 51,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,49; 33,37</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>61,08</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>44,66</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,84</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>44,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>184,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,6; 65,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,24; 49,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,33; 39,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,39; 72,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>147,9; 226,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,44; 112,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,64; 71,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,55; 292,46</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>69,2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>51,7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>44,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>272,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>134,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,82; 73,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,77; 57,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,78; 49,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,08; 31,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>207,31; 344,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>106,42; 167,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,31; 106,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,34; 48,49</t>
         </is>
       </c>
     </row>
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,84</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>51,29</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>46,17</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>33,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>125,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>141,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,0; 56,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,17; 58,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,06; 52,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,2; 39,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,97; 161,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>106,13; 189,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78,12; 128,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,23; 67,17</t>
         </is>
       </c>
     </row>
@@ -1212,42 +1212,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,65</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,25</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,46; 42,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,54; 35,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,41; 36,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,99; 31,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,99; 143,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,53; 139,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,34; 104,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,1; 71,02</t>
         </is>
       </c>
     </row>
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,87</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,87</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,27</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,24</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>145,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,7; 51,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,72; 42,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,35; 36,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,81; 42,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133,71; 159,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,41; 99,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,17; 70,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,32; 88,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,55</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,68; 41,88</t>
+          <t>30,04; 41,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,66; 39,25</t>
+          <t>26,69; 39,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 41,28</t>
+          <t>27,27; 41,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 29,87</t>
+          <t>8,97; 28,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>149,86; 281,35</t>
+          <t>147,77; 285,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,11; 187,41</t>
+          <t>96,09; 190,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,67; 166,81</t>
+          <t>83,71; 164,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 70,85</t>
+          <t>16,93; 68,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,11</t>
+          <t>27,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,03; 48,47</t>
+          <t>39,42; 48,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,42; 42,9</t>
+          <t>33,27; 42,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,39; 33,68</t>
+          <t>24,34; 34,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 32,27</t>
+          <t>20,25; 32,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,85; 124,14</t>
+          <t>85,65; 123,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,44; 91,61</t>
+          <t>62,09; 91,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,28; 60,16</t>
+          <t>38,94; 62,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,13; 52,25</t>
+          <t>28,63; 54,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,26</t>
+          <t>21,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,32; 56,18</t>
+          <t>47,65; 56,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,56; 41,35</t>
+          <t>33,06; 41,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 24,43</t>
+          <t>18,1; 25,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>104,63; 149,75</t>
+          <t>106,12; 153,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,84; 77,43</t>
+          <t>54,4; 77,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,83; 51,92</t>
+          <t>35,82; 51,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,49; 33,37</t>
+          <t>23,06; 35,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,61</t>
+          <t>24,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,6; 65,89</t>
+          <t>56,21; 65,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,24; 49,53</t>
+          <t>39,47; 49,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,33; 39,79</t>
+          <t>31,65; 40,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 72,37</t>
+          <t>21,16; 28,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>147,9; 226,38</t>
+          <t>149,8; 223,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,44; 112,47</t>
+          <t>74,45; 110,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,64; 71,6</t>
+          <t>50,29; 72,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 292,46</t>
+          <t>28,05; 41,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28,12</t>
+          <t>28,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>63,82; 73,73</t>
+          <t>64,31; 73,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,77; 57,01</t>
+          <t>46,03; 57,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,78; 49,17</t>
+          <t>39,28; 49,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 31,72</t>
+          <t>24,43; 31,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>207,31; 344,06</t>
+          <t>214,27; 343,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>106,42; 167,02</t>
+          <t>106,67; 173,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,31; 106,12</t>
+          <t>71,12; 106,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>33,34; 48,49</t>
+          <t>33,9; 48,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33,66</t>
+          <t>31,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,0; 56,62</t>
+          <t>43,33; 56,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,17; 58,11</t>
+          <t>44,76; 58,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,06; 52,56</t>
+          <t>40,01; 52,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,2; 39,6</t>
+          <t>27,3; 36,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,97; 161,94</t>
+          <t>95,17; 161,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106,13; 189,71</t>
+          <t>108,93; 186,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,12; 128,81</t>
+          <t>77,59; 125,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,23; 67,17</t>
+          <t>41,29; 61,51</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,64</t>
+          <t>25,69</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,46; 42,8</t>
+          <t>25,46; 42,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,54; 35,52</t>
+          <t>19,02; 35,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,41; 36,18</t>
+          <t>21,1; 36,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,99; 31,47</t>
+          <t>20,47; 31,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,99; 143,89</t>
+          <t>59,78; 140,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,53; 139,33</t>
+          <t>52,27; 135,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,34; 104,07</t>
+          <t>48,71; 107,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,1; 71,02</t>
+          <t>38,57; 70,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30,24</t>
+          <t>25,16</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,7; 51,97</t>
+          <t>47,68; 52,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,72; 42,01</t>
+          <t>37,79; 42,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,35; 36,43</t>
+          <t>32,19; 36,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,81; 42,85</t>
+          <t>22,8; 27,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>133,71; 159,42</t>
+          <t>132,88; 159,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,41; 99,05</t>
+          <t>83,6; 100,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,17; 70,77</t>
+          <t>58,67; 70,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,32; 88,84</t>
+          <t>33,81; 42,74</t>
         </is>
       </c>
     </row>
